--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.630992679609246</v>
+        <v>1.402536310436503</v>
       </c>
       <c r="D2" t="n">
-        <v>9.649004131844789</v>
+        <v>1.567963171424778</v>
       </c>
       <c r="E2" t="n">
-        <v>5.53596699812763</v>
+        <v>0.8995946371957402</v>
       </c>
       <c r="F2" t="n">
-        <v>4.93808087260483</v>
+        <v>0.8024381417982851</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.65777327837406</v>
+        <v>3.844388157735785</v>
       </c>
       <c r="D3" t="n">
-        <v>18.78612166858661</v>
+        <v>3.052744771145324</v>
       </c>
       <c r="E3" t="n">
-        <v>5.53596699812763</v>
+        <v>0.8995946371957402</v>
       </c>
       <c r="F3" t="n">
-        <v>4.93808087260483</v>
+        <v>0.8024381417982851</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.72861250704132</v>
+        <v>3.043399532394214</v>
       </c>
       <c r="D4" t="n">
-        <v>9.055385138137417</v>
+        <v>1.47150008494733</v>
       </c>
       <c r="E4" t="n">
-        <v>5.53596699812763</v>
+        <v>0.8995946371957402</v>
       </c>
       <c r="F4" t="n">
-        <v>4.93808087260483</v>
+        <v>0.8024381417982851</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.64738156920201</v>
+        <v>3.192699504995327</v>
       </c>
       <c r="D5" t="n">
-        <v>19.61767271816688</v>
+        <v>3.187871816702119</v>
       </c>
       <c r="E5" t="n">
-        <v>5.53596699812763</v>
+        <v>0.8995946371957402</v>
       </c>
       <c r="F5" t="n">
-        <v>4.93808087260483</v>
+        <v>0.8024381417982851</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
